--- a/AAII_Financials/Quarterly/CBUMY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CBUMY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
   <si>
     <t>CBUMY</t>
   </si>
@@ -656,77 +656,88 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +777,17 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +827,17 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +877,17 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +903,11 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +947,17 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +997,17 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1047,17 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1097,17 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1120,11 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1164,17 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1214,17 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1240,11 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1284,17 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1334,17 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1384,17 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1434,17 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1484,17 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1534,17 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1584,17 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1634,17 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1684,17 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1734,17 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1784,17 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1834,17 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1884,17 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1934,17 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1984,17 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +2034,72 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2115,11 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,377 +2135,461 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4272800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>4208000</v>
+      </c>
+      <c r="F41" s="3">
+        <v>3408700</v>
+      </c>
+      <c r="G41" s="3">
         <v>3862000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>3670600</v>
       </c>
-      <c r="F41" s="3">
-        <v>3803900</v>
-      </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>3623700</v>
+      </c>
+      <c r="J41" s="3">
         <v>3224200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="K41" s="3">
         <v>3912400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="L41" s="3">
         <v>3414000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>4543000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>3868400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>4809400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>4484800</v>
       </c>
-      <c r="N41" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R41" s="3">
         <v>3913200</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>542400</v>
+      </c>
+      <c r="E42" s="3">
+        <v>534100</v>
+      </c>
+      <c r="F42" s="3">
+        <v>929700</v>
+      </c>
+      <c r="G42" s="3">
         <v>1254800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="H42" s="3">
         <v>613000</v>
       </c>
-      <c r="F42" s="3">
-        <v>1503500</v>
-      </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
+        <v>605200</v>
+      </c>
+      <c r="J42" s="3">
         <v>1291300</v>
       </c>
-      <c r="H42" s="3">
+      <c r="K42" s="3">
         <v>1445500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="L42" s="3">
         <v>895800</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>1401300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="O42" s="3">
         <v>1391800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="P42" s="3">
         <v>968300</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>1173800</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>14750000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>14526300</v>
+      </c>
+      <c r="F43" s="3">
+        <v>13273500</v>
+      </c>
+      <c r="G43" s="3">
         <v>11665900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>13622800</v>
       </c>
-      <c r="F43" s="3">
-        <v>10752800</v>
-      </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
+        <v>13448700</v>
+      </c>
+      <c r="J43" s="3">
         <v>12374200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>11185400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>12860300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>10468900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>12011300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>11129100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>13199900</v>
       </c>
-      <c r="N43" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R43" s="3">
         <v>13077100</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>3176500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3128400</v>
+      </c>
+      <c r="F44" s="3">
+        <v>2581200</v>
+      </c>
+      <c r="G44" s="3">
         <v>3113500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>3010500</v>
       </c>
-      <c r="F44" s="3">
-        <v>2866500</v>
-      </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>2972000</v>
+      </c>
+      <c r="J44" s="3">
         <v>2322400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>3053200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>3076800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>3237300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>2979700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>3339900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>3377200</v>
       </c>
-      <c r="N44" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3">
         <v>3560200</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>498900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>491300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>463100</v>
+      </c>
+      <c r="G45" s="3">
         <v>2342200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>497500</v>
       </c>
-      <c r="F45" s="3">
-        <v>2303800</v>
-      </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
+        <v>491100</v>
+      </c>
+      <c r="J45" s="3">
         <v>521900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>2155200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>516800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>3489700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>682300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>1953800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>531400</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R45" s="3">
         <v>620100</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>23240600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>22888100</v>
+      </c>
+      <c r="F46" s="3">
+        <v>20656200</v>
+      </c>
+      <c r="G46" s="3">
         <v>22238400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>21414300</v>
       </c>
-      <c r="F46" s="3">
-        <v>21230400</v>
-      </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>21140800</v>
+      </c>
+      <c r="J46" s="3">
         <v>19733900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>21751800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>20763600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>21738800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>20942900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>22624000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>22561500</v>
       </c>
-      <c r="N46" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R46" s="3">
         <v>22344400</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5686500</v>
+      </c>
+      <c r="E47" s="3">
+        <v>5600200</v>
+      </c>
+      <c r="F47" s="3">
+        <v>5426700</v>
+      </c>
+      <c r="G47" s="3">
         <v>4972000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>5428500</v>
       </c>
-      <c r="F47" s="3">
-        <v>4833600</v>
-      </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
+        <v>5359100</v>
+      </c>
+      <c r="J47" s="3">
         <v>5087700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="K47" s="3">
         <v>4732400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="L47" s="3">
         <v>5005800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="M47" s="3">
         <v>4606900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="N47" s="3">
         <v>5185600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="O47" s="3">
         <v>4260700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="P47" s="3">
         <v>4682200</v>
       </c>
-      <c r="N47" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R47" s="3">
         <v>4919600</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>32165000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>31677200</v>
+      </c>
+      <c r="F48" s="3">
+        <v>32419700</v>
+      </c>
+      <c r="G48" s="3">
         <v>28873300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>32328300</v>
       </c>
-      <c r="F48" s="3">
-        <v>28453200</v>
-      </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
+        <v>31915300</v>
+      </c>
+      <c r="J48" s="3">
         <v>31687000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>29301800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>31678000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>28049800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>31732900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>27856900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>31211100</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R48" s="3">
         <v>32471700</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10308200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10151800</v>
+      </c>
+      <c r="F49" s="3">
+        <v>9303000</v>
+      </c>
+      <c r="G49" s="3">
         <v>12342200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="H49" s="3">
         <v>9342400</v>
       </c>
-      <c r="F49" s="3">
-        <v>11984300</v>
-      </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
+        <v>9223100</v>
+      </c>
+      <c r="J49" s="3">
         <v>8996600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="K49" s="3">
         <v>12442900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="L49" s="3">
         <v>8985700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="M49" s="3">
         <v>11951100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="N49" s="3">
         <v>8761200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="O49" s="3">
         <v>11528600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="P49" s="3">
         <v>8709800</v>
       </c>
-      <c r="N49" s="3">
-        <v>0</v>
-      </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3">
         <v>8927400</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2629,17 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2679,67 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>481700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>474400</v>
+      </c>
+      <c r="F52" s="3">
+        <v>509400</v>
+      </c>
+      <c r="G52" s="3">
         <v>935700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>513800</v>
       </c>
-      <c r="F52" s="3">
-        <v>1066200</v>
-      </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
+        <v>507200</v>
+      </c>
+      <c r="J52" s="3">
         <v>557600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>1238800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>508000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>1333800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>473700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>1374200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>510500</v>
       </c>
-      <c r="N52" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R52" s="3">
         <v>586800</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2779,67 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>73817800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>72698300</v>
+      </c>
+      <c r="F54" s="3">
+        <v>69990600</v>
+      </c>
+      <c r="G54" s="3">
         <v>71459300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>70596600</v>
       </c>
-      <c r="F54" s="3">
-        <v>69589600</v>
-      </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>69694800</v>
+      </c>
+      <c r="J54" s="3">
         <v>67680600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>71539400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>68760300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>69696000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>68947200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>69629600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>69442100</v>
       </c>
-      <c r="N54" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R54" s="3">
         <v>70948100</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2855,11 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,254 +2875,311 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>9308900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>9167700</v>
+      </c>
+      <c r="F57" s="3">
+        <v>9041000</v>
+      </c>
+      <c r="G57" s="3">
         <v>9085000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="H57" s="3">
         <v>8679600</v>
       </c>
-      <c r="F57" s="3">
-        <v>8289200</v>
-      </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
+        <v>8568700</v>
+      </c>
+      <c r="J57" s="3">
         <v>8455100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="K57" s="3">
         <v>9249100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>8899900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>8784600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>9084900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>9411800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>9623700</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R57" s="3">
         <v>9966100</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>14337400</v>
+      </c>
+      <c r="E58" s="3">
+        <v>14120000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>13340800</v>
+      </c>
+      <c r="G58" s="3">
         <v>7121800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="H58" s="3">
         <v>14535400</v>
       </c>
-      <c r="F58" s="3">
-        <v>5659000</v>
-      </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
+        <v>14349700</v>
+      </c>
+      <c r="J58" s="3">
         <v>11457600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="K58" s="3">
         <v>5042800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>10871900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="M58" s="3">
         <v>5433900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="N58" s="3">
         <v>10640100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="O58" s="3">
         <v>5507600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="P58" s="3">
         <v>10793400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>11319200</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5418100</v>
+      </c>
+      <c r="E59" s="3">
+        <v>5336000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>5149500</v>
+      </c>
+      <c r="G59" s="3">
         <v>10259200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>4939400</v>
       </c>
-      <c r="F59" s="3">
-        <v>11331600</v>
-      </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
+        <v>4876300</v>
+      </c>
+      <c r="J59" s="3">
         <v>4944800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>9128800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>5207800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>9545300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>5203600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>9455700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>5300900</v>
       </c>
-      <c r="N59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R59" s="3">
         <v>6130400</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>29069100</v>
+      </c>
+      <c r="E60" s="3">
+        <v>28628200</v>
+      </c>
+      <c r="F60" s="3">
+        <v>27534500</v>
+      </c>
+      <c r="G60" s="3">
         <v>26693000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>28157400</v>
       </c>
-      <c r="F60" s="3">
-        <v>25485200</v>
-      </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>27797700</v>
+      </c>
+      <c r="J60" s="3">
         <v>24861100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>23659600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>24981200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>23964900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>24932700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>24632500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>25721900</v>
       </c>
-      <c r="N60" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R60" s="3">
         <v>27425300</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>17178900</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16918400</v>
+      </c>
+      <c r="F61" s="3">
+        <v>14919300</v>
+      </c>
+      <c r="G61" s="3">
         <v>15568400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>14677500</v>
       </c>
-      <c r="F61" s="3">
-        <v>16058400</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
+        <v>14489900</v>
+      </c>
+      <c r="J61" s="3">
         <v>15334800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>18934800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>16837300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>17215600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>15901900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>15798800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>16205500</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3">
         <v>14263800</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G62" s="3">
         <v>1088000</v>
       </c>
-      <c r="E62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F62" s="3">
-        <v>806000</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K62" s="3">
         <v>970800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M62" s="3">
         <v>954500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O62" s="3">
         <v>1085200</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R62" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3219,17 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3269,17 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3319,67 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>47121700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>46407100</v>
+      </c>
+      <c r="F66" s="3">
+        <v>43338700</v>
+      </c>
+      <c r="G66" s="3">
         <v>44132200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>43686800</v>
       </c>
-      <c r="F66" s="3">
-        <v>43115000</v>
-      </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
+        <v>43128700</v>
+      </c>
+      <c r="J66" s="3">
         <v>41029600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>44340200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>42647200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>42889900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>41656700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>42182100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>42686200</v>
       </c>
-      <c r="N66" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R66" s="3">
         <v>42532600</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3395,11 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3439,17 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3489,17 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3539,17 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3589,67 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>13144600</v>
+        <v>11692900</v>
       </c>
       <c r="E72" s="3">
+        <v>11515600</v>
+      </c>
+      <c r="F72" s="3">
+        <v>11637300</v>
+      </c>
+      <c r="G72" s="3">
+        <v>12083200</v>
+      </c>
+      <c r="H72" s="3">
         <v>12061300</v>
       </c>
-      <c r="F72" s="3">
-        <v>11583200</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>11907200</v>
+      </c>
+      <c r="J72" s="3">
         <v>11817500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="K72" s="3">
         <v>12972700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="L72" s="3">
         <v>11258300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="M72" s="3">
         <v>11455600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="N72" s="3">
         <v>12093900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="O72" s="3">
         <v>13253700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="P72" s="3">
         <v>11760000</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R72" s="3">
         <v>12226500</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3689,17 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3739,17 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3789,67 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>15687400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>15449500</v>
+      </c>
+      <c r="F76" s="3">
+        <v>15822300</v>
+      </c>
+      <c r="G76" s="3">
         <v>16412200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>16244200</v>
       </c>
-      <c r="F76" s="3">
-        <v>15962900</v>
-      </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>16036700</v>
+      </c>
+      <c r="J76" s="3">
         <v>16364100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>16619600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>16065500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>16879500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>17369300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>17160800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>16635900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="Q76" s="3">
         <v>17927700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="R76" s="3">
         <v>17854900</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3889,72 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3994,17 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +4020,61 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>486900</v>
+      </c>
+      <c r="E83" s="3">
+        <v>480700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>1877100</v>
+      </c>
+      <c r="G83" s="3">
         <v>-1084500</v>
       </c>
-      <c r="E83" s="3">
-        <v>923400</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2006100</v>
-      </c>
       <c r="H83" s="3">
+        <v>461700</v>
+      </c>
+      <c r="I83" s="3">
+        <v>464700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>528800</v>
+      </c>
+      <c r="K83" s="3">
         <v>-1058700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>927400</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N83" s="3">
         <v>1992400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>-1021000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>492800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="Q83" s="3">
         <v>520700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="R83" s="3">
         <v>525900</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +4114,17 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +4164,17 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4214,17 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4264,17 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4314,67 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-160400</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2174000</v>
+      </c>
+      <c r="G89" s="3">
         <v>692600</v>
       </c>
-      <c r="E89" s="3">
-        <v>1037600</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-696100</v>
-      </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
+        <v>166300</v>
+      </c>
+      <c r="I89" s="3">
+        <v>164100</v>
+      </c>
+      <c r="J89" s="3">
         <v>2139900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>653100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>1236400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>-829600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>2048200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>838600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>1645600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="Q89" s="3">
         <v>-517100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="R89" s="3">
         <v>1846400</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,49 +4390,61 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-201900</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-198900</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-528700</v>
+      </c>
+      <c r="G91" s="3">
         <v>-449600</v>
       </c>
-      <c r="E91" s="3">
-        <v>-265000</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-406100</v>
-      </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
+        <v>-338200</v>
+      </c>
+      <c r="I91" s="3">
+        <v>-333900</v>
+      </c>
+      <c r="J91" s="3">
         <v>-759100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-275900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-677600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-667900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-424500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-886800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-364400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="Q91" s="3">
         <v>-855200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="R91" s="3">
         <v>-1187000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4484,17 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4534,67 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-28000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-27600</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-960900</v>
+      </c>
+      <c r="G94" s="3">
         <v>136000</v>
       </c>
-      <c r="E94" s="3">
-        <v>-63800</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-435400</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
+        <v>-252400</v>
+      </c>
+      <c r="I94" s="3">
+        <v>-249200</v>
+      </c>
+      <c r="J94" s="3">
         <v>-1374300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>147300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-1049600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-505700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-2152200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-227300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-738000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="Q94" s="3">
         <v>-737700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="R94" s="3">
         <v>-1416600</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,49 +4610,61 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>83800</v>
+      </c>
+      <c r="E96" s="3">
+        <v>82600</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G96" s="3">
         <v>1094600</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F96" s="3">
-        <v>230400</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="H96" s="3">
+        <v>83700</v>
+      </c>
+      <c r="I96" s="3">
+        <v>82700</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K96" s="3">
         <v>1155500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="L96" s="3">
         <v>42700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="M96" s="3">
         <v>224500</v>
       </c>
-      <c r="K96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3">
         <v>1240100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="P96" s="3">
         <v>186900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="Q96" s="3">
         <v>266800</v>
       </c>
-      <c r="O96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4704,17 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4754,17 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,127 +4804,163 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>582800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>573900</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-1245800</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1111400</v>
       </c>
-      <c r="E100" s="3">
-        <v>-628200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>1144200</v>
-      </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
+        <v>265400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>262100</v>
+      </c>
+      <c r="J100" s="3">
         <v>-718500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>-1040000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-731700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>1563200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>-324200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>-872600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>-841800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="Q100" s="3">
         <v>1993400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="R100" s="3">
         <v>-2376700</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>13300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="G101" s="3">
         <v>24600</v>
       </c>
-      <c r="E101" s="3">
-        <v>-32100</v>
-      </c>
-      <c r="F101" s="3">
-        <v>-10200</v>
-      </c>
-      <c r="G101" s="3">
-        <v>-8700</v>
-      </c>
       <c r="H101" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-12400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="L101" s="3">
         <v>8100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="M101" s="3">
         <v>-10800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="N101" s="3">
         <v>-17100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="O101" s="3">
         <v>18800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="P101" s="3">
         <v>10600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="Q101" s="3">
         <v>11200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="R101" s="3">
         <v>-16300</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>381400</v>
+      </c>
+      <c r="E102" s="3">
+        <v>375700</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="G102" s="3">
         <v>-298300</v>
       </c>
-      <c r="E102" s="3">
-        <v>367700</v>
-      </c>
-      <c r="F102" s="3">
-        <v>17700</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
+        <v>192800</v>
+      </c>
+      <c r="I102" s="3">
+        <v>190300</v>
+      </c>
+      <c r="J102" s="3">
         <v>31800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>-214900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-577000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>217700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-436800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>-273700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>73800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="Q102" s="3">
         <v>727800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="R102" s="3">
         <v>-1964000</v>
       </c>
     </row>
